--- a/output/topology_excel/784.xlsx
+++ b/output/topology_excel/784.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,23 +490,32 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>23814</v>
+      </c>
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>732</v>
+        <v>26904</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>61</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -504,81 +528,108 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>319470</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>832</v>
+        <v>47415</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>327</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4251</v>
+        <v>15369</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>57</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>26904</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>684</v>
+        <v>9880</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>49</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -591,81 +642,108 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>402358</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F6" t="n">
-        <v>249</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2988</v>
+        <v>9880</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>61</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>16241</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>588</v>
+        <v>102378</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>54</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>6804</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>854</v>
+        <v>92510</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>102</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -678,139 +756,184 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
-      </c>
-      <c r="G9" t="n">
-        <v>910</v>
+        <v>92510</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>70</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>402358</v>
+      </c>
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>648</v>
+        <v>102378</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>67</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>319470</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F11" t="n">
-        <v>149</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1788</v>
+        <v>46980</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1326</v>
+        <v>9540</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>86</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>9540</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>980</v>
+        <v>3330</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>49</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -823,23 +946,32 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>229</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6386</v>
+        <v>47415</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>54</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -852,23 +984,32 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>804</v>
+        <v>23814</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>126</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -881,81 +1022,108 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>249</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4440</v>
+        <v>26904</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>189</v>
+      </c>
+      <c r="J16" t="n">
+        <v>166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>806</v>
+        <v>15369</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>153</v>
+      </c>
+      <c r="J17" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" t="inlineStr">
+        <v>402358</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F18" t="n">
-        <v>324</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4212</v>
+        <v>16241</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>149</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -968,23 +1136,32 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1032</v>
+        <v>9880</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -997,81 +1174,108 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>106</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1272</v>
+        <v>102378</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>237</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>402358</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>92510</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>217</v>
+      </c>
+      <c r="J21" t="n">
         <v>14</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>588</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>402358</v>
+      </c>
+      <c r="D22" t="n">
         <v>13</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>14</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F22" t="n">
-        <v>90</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1080</v>
+        <v>9540</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>106</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1084,284 +1288,374 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>402358</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5320</v>
+        <v>3330</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>37</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>319470</v>
+      </c>
+      <c r="D24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F24" t="n">
-        <v>73</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7674</v>
+        <v>47415</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>327</v>
+      </c>
+      <c r="J24" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>319470</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>138</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3648</v>
+        <v>46980</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>324</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>47415</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>329</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4302</v>
+        <v>23814</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>189</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>47415</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>149</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1788</v>
+        <v>6804</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>54</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>47415</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>37</v>
-      </c>
-      <c r="G28" t="n">
-        <v>444</v>
+        <v>46980</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>145</v>
+      </c>
+      <c r="J28" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>23814</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1288</v>
+        <v>26904</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>177</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="inlineStr">
+        <v>23814</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F30" t="n">
-        <v>189</v>
-      </c>
-      <c r="G30" t="n">
-        <v>4914</v>
+        <v>6804</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>126</v>
+      </c>
+      <c r="J30" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>26904</v>
+      </c>
+      <c r="D31" t="n">
         <v>8</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F31" t="n">
-        <v>11</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1804</v>
+        <v>9880</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>152</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>15369</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F32" t="n">
-        <v>54</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1404</v>
+        <v>16241</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>109</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1374,139 +1668,336 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>15369</v>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F33" t="n">
+        <v>102378</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
         <v>141</v>
       </c>
-      <c r="G33" t="n">
-        <v>1692</v>
+      <c r="J33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16241</v>
+      </c>
+      <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>11</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F34" t="n">
-        <v>12</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2172</v>
+        <v>102378</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>149</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
-      </c>
-      <c r="D35" t="inlineStr">
+        <v>9880</v>
+      </c>
+      <c r="D35" t="n">
+        <v>9</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F35" t="n">
-        <v>90</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1080</v>
+        <v>6804</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>54</v>
+      </c>
+      <c r="J35" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9880</v>
+      </c>
+      <c r="D36" t="n">
         <v>11</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>12</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F36" t="n">
-        <v>312</v>
-      </c>
-      <c r="G36" t="n">
-        <v>8112</v>
+        <v>92510</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>152</v>
+      </c>
+      <c r="J36" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6804</v>
+      </c>
+      <c r="D37" t="n">
         <v>11</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="F37" t="n">
+        <v>92510</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>126</v>
+      </c>
+      <c r="J37" t="n">
         <v>13</v>
       </c>
-      <c r="D37" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>102378</v>
+      </c>
+      <c r="D38" t="n">
+        <v>14</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>90</v>
+      </c>
+      <c r="J38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>46980</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>312</v>
+      </c>
+      <c r="J39" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>11</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
+      <c r="F40" t="n">
+        <v>9540</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>90</v>
       </c>
-      <c r="G37" t="n">
-        <v>1260</v>
+      <c r="J40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9540</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>90</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/784.xlsx
+++ b/output/topology_excel/784.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">

--- a/output/topology_excel/784.xlsx
+++ b/output/topology_excel/784.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
         <v>8</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>166</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F18" t="n">
         <v>12</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="n">
         <v>11</v>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>327</v>
+        <v>152</v>
       </c>
       <c r="F24" t="n">
         <v>13</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>324</v>
+        <v>217</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="F26" t="n">
         <v>26</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
         <v>9</v>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1073,15 +1073,15 @@
         <v>177</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,15 +1092,15 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
         <v>8</v>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="F31" t="n">
         <v>12</v>
@@ -1125,7 +1125,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1169,7 +1169,7 @@
         <v>7</v>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
         <v>12</v>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="F35" t="n">
         <v>12</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -1257,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>327</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="F39" t="n">
         <v>26</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,32 +1312,120 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>145</v>
+      </c>
+      <c r="F41" t="n">
         <v>13</v>
       </c>
-      <c r="B41" t="n">
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B42" t="n">
+        <v>13</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>324</v>
+      </c>
+      <c r="F42" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>14</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>90</v>
-      </c>
-      <c r="F41" t="n">
-        <v>12</v>
+      <c r="B43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>126</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>340</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>155</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/784.xlsx
+++ b/output/topology_excel/784.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
